--- a/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
+++ b/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="101">
   <si>
     <t>工作表目录</t>
   </si>
@@ -68,7 +68,7 @@
     <t>国家管网集团上海区域总部后勤物业服务项目</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年07月）</t>
+    <t>合计预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -117,7 +117,7 @@
     <t>一、 营业收入</t>
   </si>
   <si>
-    <t>餐饮宴会厅收入较同期减少155万元，中餐厅较同期减少80万元，外接项目结束，租赁户减少，截止至7月空置率29.11%。</t>
+    <t>餐饮宴会厅收入较同期减少155万元，中餐厅较同期减少80万元，外接项目结束，租赁户减少，截止至8月空置率29.11%。</t>
   </si>
   <si>
     <t>受宴会厅装修改造因素影响，客房收入减少144万元，宴会收入较预算减少385万元，中餐厅较预算减少113万元，经营性租赁减少60万元。外接项目结束428万元。</t>
@@ -281,10 +281,10 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_合并预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>租赁户减少，截止至7月空置率29.11%。</t>
+    <t>上海酒店租赁项目_合并预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>租赁户减少，截止至8月空置率29.11%。</t>
   </si>
   <si>
     <t>租赁收入减少，房产税下降。</t>
@@ -293,19 +293,22 @@
     <t>预算估计不足。</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_222200150213预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>上海酒店租赁项目_222200150214预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>上海酒店预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>餐饮宴会厅收入较同期减少155万元，中餐厅较同期减少80万元</t>
-  </si>
-  <si>
-    <t>受宴会厅装修改造因素影响，客房收入减少144万元，宴会收入较预算减少385万元，中餐厅较预算减少113万元，经营性租赁减少60万元。</t>
+    <t>上海酒店租赁项目_222200150213预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>上海酒店租赁项目_222200150214预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>上海酒店预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>餐饮宴会厅收入较同期减少182万元，中餐厅较同期减少87万元，客房收入减少85万元</t>
+  </si>
+  <si>
+    <t>受宴会厅装修改造因素影响，客房收入减少162万元，宴会收入较预算减少441万元，中餐厅较预算减少125万元，经营性租赁减少60万元。</t>
+  </si>
+  <si>
+    <t>确认跨期外包费用约50万，财务部组建增加人工约45万元。</t>
   </si>
   <si>
     <t>宴会厅装修改造LED设备使用减少。</t>
@@ -314,22 +317,22 @@
     <t>应收账款回收速度加快。</t>
   </si>
   <si>
-    <t>上海酒店能源转售项目预算执行分析（2026年07月）</t>
+    <t>上海酒店能源转售项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>租赁户减少，能源使用下降。</t>
   </si>
   <si>
-    <t>中石化海洋局商城路基地配餐项目预算执行分析（2026年07月）</t>
+    <t>中石化海洋局商城路基地配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目已结束</t>
   </si>
   <si>
-    <t>中石化海洋局商城路基地物业服务项目预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>国家管网集团上海区域总部后勤配餐项目预算执行分析（2026年07月）</t>
+    <t>中石化海洋局商城路基地物业服务项目预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>国家管网集团上海区域总部后勤配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>国家管网项目4月3日结束，去年同期为整年。</t>
@@ -338,7 +341,7 @@
     <t>国家管网项目4月3日结束，预算为整年。</t>
   </si>
   <si>
-    <t>国家管网集团上海区域总部后勤物业服务项目预算执行分析（2026年07月）</t>
+    <t>国家管网集团上海区域总部后勤物业服务项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>外购燃料为代收代付。</t>
@@ -849,7 +852,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -919,7 +922,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -939,7 +942,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -1049,7 +1052,7 @@
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -1177,7 +1180,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -1197,7 +1200,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
@@ -1217,7 +1220,7 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12"/>
@@ -1255,7 +1258,7 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="12"/>
@@ -1275,7 +1278,7 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12"/>
@@ -1630,7 +1633,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1700,11 +1703,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -1722,11 +1725,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -1744,11 +1747,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -1766,11 +1769,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -1788,11 +1791,11 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
@@ -1990,11 +1993,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -2419,7 +2422,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2489,11 +2492,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -2621,7 +2624,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -2747,11 +2750,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -2769,11 +2772,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -6807,7 +6810,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
@@ -6851,11 +6854,11 @@
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -7007,7 +7010,7 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12"/>
@@ -7254,7 +7257,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7324,11 +7327,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -7472,11 +7475,11 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -8027,7 +8030,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8097,7 +8100,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -8117,7 +8120,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -8137,7 +8140,7 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -8157,7 +8160,7 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -8357,7 +8360,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -8377,7 +8380,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>

--- a/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
+++ b/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
@@ -9,15 +9,15 @@
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="上海酒店租赁项目_合并" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="上海酒店租赁项目_222200150213" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="上海酒店租赁项目_222200150214" state="visible" r:id="rId8"/>
+    <sheet sheetId="4" name="上海酒店租赁_合并" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="上海酒店租赁_222200150213" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="上海酒店租赁_222200150214" state="visible" r:id="rId8"/>
     <sheet sheetId="7" name="上海酒店" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="上海酒店能源转售项目" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="中石化海洋局商城路基地配餐项目" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="中石化海洋局商城路基地物业服务项目" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="国家管网集团上海区域总部后勤配餐项目" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="国家管网集团上海区域总部后勤物业服务项目" state="visible" r:id="rId14"/>
+    <sheet sheetId="8" name="上海酒店能源" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="商城路配餐TERM" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="商城路物业TERM" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="管网配餐TERM" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="管网物业TERM" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -41,31 +41,31 @@
     <t>合计</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_合并</t>
-  </si>
-  <si>
-    <t>上海酒店租赁项目_222200150213</t>
-  </si>
-  <si>
-    <t>上海酒店租赁项目_222200150214</t>
+    <t>上海酒店租赁_合并</t>
+  </si>
+  <si>
+    <t>上海酒店租赁_222200150213</t>
+  </si>
+  <si>
+    <t>上海酒店租赁_222200150214</t>
   </si>
   <si>
     <t>上海酒店</t>
   </si>
   <si>
-    <t>上海酒店能源转售项目</t>
-  </si>
-  <si>
-    <t>中石化海洋局商城路基地配餐项目</t>
-  </si>
-  <si>
-    <t>中石化海洋局商城路基地物业服务项目</t>
-  </si>
-  <si>
-    <t>国家管网集团上海区域总部后勤配餐项目</t>
-  </si>
-  <si>
-    <t>国家管网集团上海区域总部后勤物业服务项目</t>
+    <t>上海酒店能源</t>
+  </si>
+  <si>
+    <t>商城路配餐TERM</t>
+  </si>
+  <si>
+    <t>商城路物业TERM</t>
+  </si>
+  <si>
+    <t>管网配餐TERM</t>
+  </si>
+  <si>
+    <t>管网物业TERM</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -281,7 +281,7 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_合并预算执行分析（2026年08月）</t>
+    <t>上海酒店租赁_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>租赁户减少，截止至8月空置率29.11%。</t>
@@ -293,10 +293,10 @@
     <t>预算估计不足。</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_222200150213预算执行分析（2026年08月）</t>
-  </si>
-  <si>
-    <t>上海酒店租赁项目_222200150214预算执行分析（2026年08月）</t>
+    <t>上海酒店租赁_222200150213预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>上海酒店租赁_222200150214预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上海酒店预算执行分析（2026年08月）</t>
@@ -317,22 +317,22 @@
     <t>应收账款回收速度加快。</t>
   </si>
   <si>
-    <t>上海酒店能源转售项目预算执行分析（2026年08月）</t>
+    <t>上海酒店能源预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>租赁户减少，能源使用下降。</t>
   </si>
   <si>
-    <t>中石化海洋局商城路基地配餐项目预算执行分析（2026年08月）</t>
+    <t>商城路配餐TERM预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目已结束</t>
   </si>
   <si>
-    <t>中石化海洋局商城路基地物业服务项目预算执行分析（2026年08月）</t>
-  </si>
-  <si>
-    <t>国家管网集团上海区域总部后勤配餐项目预算执行分析（2026年08月）</t>
+    <t>商城路物业TERM预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>管网配餐TERM预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>国家管网项目4月3日结束，去年同期为整年。</t>
@@ -341,7 +341,7 @@
     <t>国家管网项目4月3日结束，预算为整年。</t>
   </si>
   <si>
-    <t>国家管网集团上海区域总部后勤物业服务项目预算执行分析（2026年08月）</t>
+    <t>管网物业TERM预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>外购燃料为代收代付。</t>
@@ -3230,7 +3230,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f>HYPERLINK("#'上海酒店租赁项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'上海酒店租赁_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>HYPERLINK("#'上海酒店租赁项目_222200150213'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'上海酒店租赁_222200150213'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'上海酒店租赁项目_222200150214'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'上海酒店租赁_222200150214'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'上海酒店能源转售项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'上海酒店能源'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>HYPERLINK("#'中石化海洋局商城路基地配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'商城路配餐TERM'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>HYPERLINK("#'中石化海洋局商城路基地物业服务项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'商城路物业TERM'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>HYPERLINK("#'国家管网集团上海区域总部后勤配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'管网配餐TERM'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>HYPERLINK("#'国家管网集团上海区域总部后勤物业服务项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'管网物业TERM'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
